--- a/laporan_padel_dki_jakarta_2026-10-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-29.xlsx
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.315.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.878.000</t>
+          <t>Rp2.977.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-29.xlsx
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.168.000</t>
+          <t>Rp1.344.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.629.000</t>
+          <t>Rp12.959.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.010.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.640.000</t>
+          <t>Rp4.130.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp11.920.000</t>
+          <t>Rp12.318.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.525.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>54</v>
       </c>
       <c r="D48" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp420.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp968.000</t>
+          <t>Rp1.056.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.410.000</t>
+          <t>Rp5.585.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp5.190.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3520,16 +3520,16 @@
         <v>54</v>
       </c>
       <c r="D100" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.215.000</t>
+          <t>Rp729.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.034.000</t>
+          <t>Rp3.734.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.185.000</t>
+          <t>Rp6.320.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.399.000</t>
+          <t>Rp1.599.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.243.000</t>
+          <t>Rp1.944.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp16.035.000</t>
+          <t>Rp16.310.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp555.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.784.000</t>
+          <t>Rp5.184.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>84</v>
       </c>
       <c r="D50" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.450.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp760.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.570.000</t>
+          <t>Rp4.720.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.175.000</t>
+          <t>Rp2.290.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp150.000</t>
+          <t>Rp125.000 - Rp165.000</t>
         </is>
       </c>
     </row>
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp35.530.000</t>
+          <t>Rp35.880.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp4.860.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.940.000</t>
+          <t>Rp10.165.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp306.000</t>
+          <t>Rp444.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.395.000</t>
+          <t>Rp3.670.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp8.169.000</t>
+          <t>Rp8.309.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.910.000</t>
+          <t>Rp4.480.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp13.500.000</t>
+          <t>Rp14.400.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp21.500.000</t>
+          <t>Rp21.925.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.885.000</t>
+          <t>Rp10.930.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.605.000</t>
+          <t>Rp6.445.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>81</v>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.495.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.570.000</t>
+          <t>Rp4.785.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.675.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.220.000</t>
+          <t>Rp4.395.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D34" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.095.000</t>
+          <t>Rp5.295.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.572.000</t>
+          <t>Rp2.697.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-29.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.446.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.898.985</t>
+          <t>Rp6.957.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.485.000</t>
+          <t>Rp11.985.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.697.000</t>
+          <t>Rp11.297.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.010.000</t>
+          <t>Rp3.260.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.130.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.336.000</t>
+          <t>Rp6.912.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.056.000</t>
+          <t>Rp1.232.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp149.000</t>
+          <t>Rp349.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp225.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp7.160.000</t>
+          <t>Rp7.380.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.197.000</t>
+          <t>Rp2.395.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.490.000</t>
+          <t>Rp3.686.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp4.240.000</t>
+          <t>Rp4.540.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp5.585.000</t>
+          <t>Rp5.735.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp775.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>85</v>
       </c>
       <c r="D94" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp647.000</t>
+          <t>Rp946.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.102.000</t>
+          <t>Rp12.672.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.165.000</t>
+          <t>Rp5.315.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.944.000</t>
+          <t>Rp2.144.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp16.310.000</t>
+          <t>Rp16.810.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp8.255.000</t>
+          <t>Rp8.805.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp12.450.000</t>
+          <t>Rp12.200.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.720.000</t>
+          <t>Rp4.870.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>84</v>
       </c>
       <c r="D68" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp9.700.000</t>
+          <t>Rp10.050.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.290.000</t>
+          <t>Rp2.370.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp35.880.000</t>
+          <t>Rp36.830.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.860.000</t>
+          <t>Rp5.220.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp9.075.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.760.000</t>
+          <t>Rp9.960.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp10.245.000</t>
+          <t>Rp11.005.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.650.000</t>
+          <t>Rp7.225.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.448.500</t>
+          <t>Rp15.723.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.817.000</t>
+          <t>Rp7.375.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp2.435.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp8.850.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.923.000</t>
+          <t>Rp7.155.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp878.000</t>
+          <t>Rp1.038.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.120.000</t>
+          <t>Rp6.620.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp7.475.000</t>
+          <t>Rp7.670.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp14.400.000</t>
+          <t>Rp14.600.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.156.000</t>
+          <t>Rp4.792.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.875.000</t>
+          <t>Rp7.025.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.575.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.930.000</t>
+          <t>Rp11.450.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.180.000</t>
+          <t>Rp5.560.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>81</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.999.990</t>
+          <t>Rp4.124.990</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.415.000</t>
+          <t>Rp5.804.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp19.260.000</t>
+          <t>Rp20.220.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp4.455.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.024.993</t>
+          <t>Rp4.399.993</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp290.000</t>
+          <t>Rp580.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.525.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.586.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.955.000</t>
+          <t>Rp3.155.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D39" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-29.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.328.000</t>
+          <t>Rp2.427.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp14.040.000</t>
+          <t>Rp15.240.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.347.000</t>
+          <t>Rp1.546.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.344.000</t>
+          <t>Rp1.074.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.985.000</t>
+          <t>Rp12.235.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.959.000</t>
+          <t>Rp13.234.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.912.000</t>
+          <t>Rp3.612.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.729.000</t>
+          <t>Rp1.944.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.260.000</t>
+          <t>Rp3.490.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.798.000</t>
+          <t>Rp2.502.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.590.000</t>
+          <t>Rp5.160.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.070.000</t>
+          <t>Rp2.265.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.225.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.912.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>30</v>
       </c>
       <c r="D53" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp710.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp349.000</t>
+          <t>Rp498.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp725.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp2.180.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp3.295.000</t>
+          <t>Rp3.755.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.686.000</t>
+          <t>Rp3.586.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp6.410.000</t>
+          <t>Rp6.347.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp545.000</t>
+          <t>Rp885.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.590.000</t>
+          <t>Rp2.286.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp7.925.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.550.900</t>
+          <t>Rp2.951.300</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>42</v>
       </c>
       <c r="D93" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp693.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp8.056.000</t>
+          <t>Rp8.554.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp3.185.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp795.000</t>
+          <t>Rp1.193.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3520,16 +3520,16 @@
         <v>54</v>
       </c>
       <c r="D100" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp729.000</t>
+          <t>Rp972.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.672.000</t>
+          <t>Rp13.256.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.315.000</t>
+          <t>Rp5.465.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.599.000</t>
+          <t>Rp1.999.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.560.000</t>
+          <t>Rp8.370.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.940.000</t>
+          <t>Rp3.135.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.994.000</t>
+          <t>Rp2.343.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp16.810.000</t>
+          <t>Rp17.235.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp3.030.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp895.000</t>
+          <t>Rp716.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp15.650.000</t>
+          <t>Rp16.100.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.450.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp328.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp7.600.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.370.000</t>
+          <t>Rp2.535.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp580.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.085.000</t>
+          <t>Rp19.745.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.220.000</t>
+          <t>Rp4.920.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp300.000</t>
+          <t>Rp180.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -6257,16 +6257,16 @@
         <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.020.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6474,16 +6474,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6536,16 +6536,16 @@
         <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.994.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.960.000</t>
+          <t>Rp10.520.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp8.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp444.000</t>
+          <t>Rp643.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.005.000</t>
+          <t>Rp11.505.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.225.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.741.000</t>
+          <t>Rp8.191.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.670.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.435.000</t>
+          <t>Rp2.135.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.683.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.400.000</t>
+          <t>Rp21.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.155.000</t>
+          <t>Rp6.455.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.975.000</t>
+          <t>Rp7.485.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.038.000</t>
+          <t>Rp778.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp975.000</t>
+          <t>Rp1.325.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp7.670.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp14.600.000</t>
+          <t>Rp15.000.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.792.000</t>
+          <t>Rp5.080.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp2.092.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp21.925.000</t>
+          <t>Rp23.325.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.998.000</t>
+          <t>Rp2.798.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp11.450.000</t>
+          <t>Rp12.110.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp26.300.000</t>
+          <t>Rp26.450.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp2.660.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.656.000</t>
+          <t>Rp8.354.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.445.000</t>
+          <t>Rp7.365.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.037.000</t>
+          <t>Rp2.542.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp880.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.640.000</t>
+          <t>Rp5.395.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.124.990</t>
+          <t>Rp4.649.988</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.455.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.906.000</t>
+          <t>Rp1.707.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.399.993</t>
+          <t>Rp4.849.992</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.610.000</t>
+          <t>Rp1.865.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D34" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.295.000</t>
+          <t>Rp5.694.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.155.000</t>
+          <t>Rp3.905.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D39" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-29.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-29.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.957.986</t>
+          <t>Rp7.253.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.234.000</t>
+          <t>Rp13.312.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.612.000</t>
+          <t>Rp3.772.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1192,14 +1192,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.160.000</t>
+          <t>Rp5.285.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.565.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>76</v>
       </c>
       <c r="D44" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.520.000</t>
+          <t>Rp9.820.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp5.735.000</t>
+          <t>Rp5.490.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp2.286.000</t>
+          <t>Rp2.385.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3520,16 +3520,16 @@
         <v>54</v>
       </c>
       <c r="D100" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.135.000</t>
+          <t>Rp10.530.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp8.805.000</t>
+          <t>Rp9.080.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp12.200.000</t>
+          <t>Rp12.450.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.870.000</t>
+          <t>Rp5.258.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5834,16 +5834,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp10.450.000</t>
+          <t>Rp11.150.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.520.000</t>
+          <t>Rp10.440.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp643.000</t>
+          <t>Rp841.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.505.000</t>
+          <t>Rp11.780.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.135.000</t>
+          <t>Rp1.935.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.900.000</t>
+          <t>Rp22.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.455.000</t>
+          <t>Rp6.779.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.480.000</t>
+          <t>Rp4.605.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp15.000.000</t>
+          <t>Rp15.375.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp580.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.849.992</t>
+          <t>Rp5.099.992</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.905.000</t>
+          <t>Rp4.055.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
